--- a/db/export/excel_template.xlsx
+++ b/db/export/excel_template.xlsx
@@ -9,9 +9,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'МК'!$A$4:$BZ$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Рождения'!$A$2:$BC$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Браки'!$A$2:$BK$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Смерти'!$A$2:$BC$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Рождения'!$A$2:$BE$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Браки'!$A$2:$BM$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Смерти'!$A$2:$BE$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -8832,7 +8832,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:BE3"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.625" style="15" customWidth="1"/>
@@ -8890,6 +8890,8 @@
     <col min="53" max="53" width="8.875" style="16"/>
     <col min="54" max="54" width="8.875" style="16"/>
     <col min="55" max="55" width="8.875" style="16"/>
+    <col min="56" max="56" width="8.875" style="16" customWidth="1"/>
+    <col min="57" max="57" width="8.875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9140,6 +9142,16 @@
           <t xml:space="preserve">Прим.</t>
         </is>
       </c>
+      <c r="BD1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл</t>
+        </is>
+      </c>
+      <c r="BE1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Путь к файлу</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
@@ -9381,6 +9393,16 @@
       <c r="BC2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Церковнослужитель 3</t>
+        </is>
+      </c>
+      <c r="BD2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
+        </is>
+      </c>
+      <c r="BE2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
         </is>
       </c>
     </row>
@@ -9440,9 +9462,11 @@
       <c r="BA3" s="16"/>
       <c r="BB3" s="16"/>
       <c r="BC3" s="16"/>
+      <c r="BD3" s="16"/>
+      <c r="BE3" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BC3"/>
+  <autoFilter ref="A2:BE3"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -9453,7 +9477,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK3"/>
+  <dimension ref="A1:BM3"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.625" style="15" customWidth="1"/>
@@ -9519,6 +9543,8 @@
     <col min="61" max="61" width="8.875" style="16"/>
     <col min="62" max="62" width="8.875" style="16"/>
     <col min="63" max="63" width="8.875" style="16"/>
+    <col min="64" max="64" width="12.625" style="16" customWidth="1"/>
+    <col min="65" max="65" width="12.625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9809,6 +9835,16 @@
           <t xml:space="preserve">Прим.</t>
         </is>
       </c>
+      <c r="BL1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл</t>
+        </is>
+      </c>
+      <c r="BM1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Путь к файлу</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
@@ -10094,6 +10130,16 @@
       <c r="BK2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Поручитель 6</t>
+        </is>
+      </c>
+      <c r="BL2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
+        </is>
+      </c>
+      <c r="BM2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
         </is>
       </c>
     </row>
@@ -10161,9 +10207,11 @@
       <c r="BI3" s="16"/>
       <c r="BJ3" s="16"/>
       <c r="BK3" s="16"/>
+      <c r="BL3" s="16"/>
+      <c r="BM3" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BK3"/>
+  <autoFilter ref="A2:BM3"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -10174,7 +10222,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:BE3"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.625" style="15" customWidth="1"/>
@@ -10232,6 +10280,8 @@
     <col min="53" max="53" width="8.875" style="16"/>
     <col min="54" max="54" width="8.875" style="16"/>
     <col min="55" max="55" width="8.875" style="16"/>
+    <col min="56" max="56" width="0.625" style="16" customWidth="1"/>
+    <col min="57" max="57" width="0.625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10482,6 +10532,16 @@
           <t xml:space="preserve">Прим.</t>
         </is>
       </c>
+      <c r="BD1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл</t>
+        </is>
+      </c>
+      <c r="BE1" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Путь к файлу</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
@@ -10731,6 +10791,16 @@
       <c r="BC2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Церковнослужитель 3</t>
+        </is>
+      </c>
+      <c r="BD2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
+        </is>
+      </c>
+      <c r="BE2" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Скан</t>
         </is>
       </c>
     </row>
@@ -10790,9 +10860,11 @@
       <c r="BA3" s="16"/>
       <c r="BB3" s="16"/>
       <c r="BC3" s="16"/>
+      <c r="BD3" s="16"/>
+      <c r="BE3" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BC3"/>
+  <autoFilter ref="A2:BE3"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.2" footer="0.2"/>
 </worksheet>
 </file>